--- a/output_plant/stomata_Intermediate_steinthorsdottir_2021.xlsx
+++ b/output_plant/stomata_Intermediate_steinthorsdottir_2021.xlsx
@@ -619,7 +619,7 @@
   </si>
   <si>
     <t xml:space="preserve">U-Pb zircon ages from interbedded volcanic ashes at the P-33 type locality; reported in Hofig et al., 2021, Geology, 
-https://doi.org/10.1130/G48901.1; this age supercedes the age reported in Steinthorsdottir et al., 2021 (15.9 Ma)</t>
+https://doi.org/10.1130/G48901.1; this age supercedes the age reported in Steinthorsdottir et al., 2021 (15.9 Ma); better constrained radiometric ages based on ash interbedded at the P-33 locality</t>
   </si>
   <si>
     <t xml:space="preserve">Betulaceae / Betula</t>
